--- a/docs/Mapping_casi_uso/cittadinanza/Citt_019.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_019.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="177">
   <si>
     <t>Sezione</t>
   </si>
@@ -285,6 +285,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Madre</t>
@@ -595,11 +601,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.00390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="49.65234375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
@@ -1483,19 +1489,19 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="C39" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>10</v>
@@ -1506,19 +1512,19 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -1529,19 +1535,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
@@ -1552,19 +1558,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1575,19 +1581,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1598,19 +1604,19 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -1621,19 +1627,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E45" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -1644,19 +1650,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
@@ -1667,19 +1673,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -1690,19 +1696,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -1713,19 +1719,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -1736,19 +1742,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -1759,19 +1765,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1782,19 +1788,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1805,19 +1811,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1828,19 +1834,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1851,19 +1857,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
@@ -1874,19 +1880,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1897,19 +1903,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -1920,19 +1926,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1943,19 +1949,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1966,19 +1972,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1989,19 +1995,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -2012,19 +2018,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2035,7 +2041,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>111</v>
@@ -2044,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>112</v>
@@ -2058,7 +2064,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>113</v>
@@ -2067,7 +2073,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>114</v>
@@ -2081,19 +2087,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2104,19 +2110,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2127,19 +2133,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2150,19 +2156,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2173,19 +2179,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2196,7 +2202,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>117</v>
@@ -2205,10 +2211,10 @@
         <v>33</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2219,19 +2225,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2242,19 +2248,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2265,19 +2271,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2288,19 +2294,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2311,19 +2317,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2334,19 +2340,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2357,19 +2363,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2380,19 +2386,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2403,19 +2409,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2426,19 +2432,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2449,19 +2455,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2472,19 +2478,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2495,19 +2501,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2518,19 +2524,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2541,19 +2547,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2564,19 +2570,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2587,19 +2593,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2610,19 +2616,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2633,19 +2639,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2656,19 +2662,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2679,19 +2685,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2702,19 +2708,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2725,19 +2731,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2748,19 +2754,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2771,7 +2777,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>111</v>
@@ -2780,7 +2786,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>112</v>
@@ -2794,7 +2800,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>113</v>
@@ -2803,7 +2809,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>114</v>
@@ -2817,19 +2823,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2840,19 +2846,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2863,19 +2869,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2886,19 +2892,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2909,19 +2915,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2932,7 +2938,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>117</v>
@@ -2941,10 +2947,10 @@
         <v>33</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2955,53 +2961,53 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="E103" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E104" s="2" t="s">
+      <c r="F104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>130</v>
@@ -3010,7 +3016,7 @@
         <v>33</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>131</v>
@@ -3019,12 +3025,12 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>132</v>
@@ -3033,7 +3039,7 @@
         <v>33</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>133</v>
@@ -3042,12 +3048,12 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>134</v>
@@ -3056,7 +3062,7 @@
         <v>33</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>135</v>
@@ -3065,12 +3071,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>136</v>
@@ -3079,44 +3085,44 @@
         <v>33</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>139</v>
@@ -3125,44 +3131,44 @@
         <v>33</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>142</v>
@@ -3171,7 +3177,7 @@
         <v>33</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>143</v>
@@ -3180,12 +3186,12 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>144</v>
@@ -3194,7 +3200,7 @@
         <v>33</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>145</v>
@@ -3203,12 +3209,12 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>146</v>
@@ -3217,7 +3223,7 @@
         <v>33</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>147</v>
@@ -3226,44 +3232,44 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B116" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>153</v>
@@ -3277,7 +3283,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>154</v>
@@ -3286,7 +3292,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>155</v>
@@ -3300,7 +3306,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>156</v>
@@ -3309,7 +3315,7 @@
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>157</v>
@@ -3323,7 +3329,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>158</v>
@@ -3332,7 +3338,7 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>159</v>
@@ -3346,16 +3352,16 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>161</v>
@@ -3369,7 +3375,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>162</v>
@@ -3378,7 +3384,7 @@
         <v>33</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>163</v>
@@ -3392,7 +3398,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>164</v>
@@ -3401,7 +3407,7 @@
         <v>33</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>165</v>
@@ -3415,7 +3421,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>166</v>
@@ -3424,7 +3430,7 @@
         <v>33</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>167</v>
@@ -3438,19 +3444,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3461,19 +3467,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D125" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3484,16 +3490,16 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>153</v>
@@ -3507,7 +3513,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>154</v>
@@ -3516,7 +3522,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>155</v>
@@ -3530,7 +3536,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>156</v>
@@ -3539,7 +3545,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>157</v>
@@ -3553,7 +3559,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>158</v>
@@ -3562,7 +3568,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>159</v>
@@ -3576,16 +3582,16 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>161</v>
@@ -3599,7 +3605,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>162</v>
@@ -3608,7 +3614,7 @@
         <v>33</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>163</v>
@@ -3622,7 +3628,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>164</v>
@@ -3631,7 +3637,7 @@
         <v>33</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>165</v>
@@ -3645,7 +3651,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>166</v>
@@ -3654,7 +3660,7 @@
         <v>33</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>167</v>
@@ -3668,19 +3674,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3691,7 +3697,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>173</v>
@@ -3700,7 +3706,7 @@
         <v>33</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>174</v>
@@ -3709,6 +3715,29 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" s="2" t="s">
         <v>18</v>
       </c>
     </row>
